--- a/etf_holdings/2026-10-20_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,7 +509,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -518,16 +518,16 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.42%921,000</t>
+          <t>6.69%921,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.69%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.94%1,166,000</t>
+          <t>6.17%1,166,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>6.17%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1120</v>
+        <v>1055</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.69%2,482,000</t>
+          <t>6.08%2,482,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>6.08%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1525</v>
+        <v>1545</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.49%1,663,000</t>
+          <t>5.55%1,663,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.55%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1975</v>
+        <v>1970</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.26%1,241,000</t>
+          <t>5.51%1,255,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1241000</v>
+        <v>1255000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2005</v>
+        <v>1925</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.23%1,255,000</t>
+          <t>5.36%1,241,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.36%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1255000</v>
+        <v>1241000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,33 +875,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5125</v>
+        <v>4945</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.16%475,000</t>
+          <t>4.71%420,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>475000</v>
+        <v>420000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6245</v>
+        <v>5975</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.35%323,000</t>
+          <t>4.41%323,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.35%</t>
+          <t>4.41%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>0%154</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5235</v>
+        <v>154</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.99%364,000</t>
+          <t>4.25%12,620,868</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>364000</v>
+        <v>12620868</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9920</v>
+        <v>4900</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.83%183,000</t>
+          <t>4.17%364,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>4.17%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>183000</v>
+        <v>364000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+10%154</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>154</v>
+        <v>10100</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.72%12,620,868</t>
+          <t>3.97%183,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>12620868</v>
+        <v>183000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.39%5,245,000</t>
+          <t>3.48%5,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.68%7830</t>
+          <t>-1.09%7745</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.68%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7830</v>
+        <v>7745</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.18%202,000</t>
+          <t>3.46%202,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>-5.96%489</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1380</v>
+        <v>489</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.87%1,007,000</t>
+          <t>3.05%2,682,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1007000</v>
+        <v>2682000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:49</t>
+          <t>2026-10-20 22:20:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>982</v>
+        <v>1305</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.81%1,334,013</t>
+          <t>3.04%1,007,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>3.04%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1334013</v>
+        <v>1007000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.26%520</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.26%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>520</v>
+        <v>945</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.79%2,682,000</t>
+          <t>2.87%1,334,013</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2682000</v>
+        <v>1334013</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.37%180</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>180</v>
+        <v>1185</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.76%7,185,000</t>
+          <t>2.08%759,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>7185000</v>
+        <v>759000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>6584南俊國際</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-1.8%464</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1250</v>
+        <v>464</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.99%759,000</t>
+          <t>1.97%1,904,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>759000</v>
+        <v>1904000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,25 +1602,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6584南俊國際</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.53%472.5</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>472.5</v>
+        <v>1550</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.90%1,904,000</t>
+          <t>1.90%533,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1629,11 +1629,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1904000</v>
+        <v>533000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1630</v>
+        <v>2000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.81%533,000</t>
+          <t>1.87%426,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>533000</v>
+        <v>426000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2005</v>
+        <v>1925</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.79%426,000</t>
+          <t>1.82%440,675</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>426000</v>
+        <v>440675</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.9%767</t>
+          <t>-2.35%749</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.76%1,079,000</t>
+          <t>1.81%1,079,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1885</v>
+        <v>189</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.71%440,675</t>
+          <t>1.75%4,454,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>440675</v>
+        <v>4454000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.60%179,000</t>
+          <t>1.65%179,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.8%547</t>
+          <t>0%547</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.41%1,200,000</t>
+          <t>1.44%1,200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.07%755,000</t>
+          <t>1.11%755,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.11%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6560</v>
+        <v>6650</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.98%69,000</t>
+          <t>0.99%69,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.35%1405</t>
+          <t>-6.05%1320</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>-6.05%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1405</v>
+        <v>1320</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.82%278,000</t>
+          <t>0.85%278,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.69%200,000</t>
+          <t>0.72%200,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:50</t>
+          <t>2026-10-20 22:20:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-8.81%735</t>
+          <t>-3.88%4960</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.81%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>735</v>
+        <v>4960</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.62%367,000</t>
+          <t>0.64%57,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>367000</v>
+        <v>57000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0%5160</t>
+          <t>+8.03%794</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5160</v>
+        <v>794</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.62%57,000</t>
+          <t>0.59%367,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>57000</v>
+        <v>367000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.84%102.5</t>
+          <t>-3.32%99.1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>102.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.45%2,032,000</t>
+          <t>0.46%2,032,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.41%970</t>
+          <t>+1.13%981</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.43%206,000</t>
+          <t>0.44%206,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.54%352</t>
+          <t>+0.85%355</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.40%534,000</t>
+          <t>0.41%534,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,34 +2578,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.9%1100</t>
+          <t>-0.76%262</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.76%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1100</v>
+        <v>262</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.39%166,000</t>
+          <t>0.40%693,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>166000</v>
+        <v>693000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.19%264</t>
+          <t>-0.91%1090</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>264</v>
+        <v>1090</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.39%693,000</t>
+          <t>0.40%166,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>693000</v>
+        <v>166000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>15980</v>
+        <v>2490</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.38%11,000</t>
+          <t>0.39%69,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>11000</v>
+        <v>69000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.07%663</t>
+          <t>-2.56%646</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.38%266,000</t>
+          <t>0.39%266,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.83%1130</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.83%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1130</v>
+        <v>15900</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.38%152,952</t>
+          <t>0.38%11,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>152952</v>
+        <v>11000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>5289宜鼎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>-2.65%1100</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2570</v>
+        <v>1100</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.37%69,000</t>
+          <t>0.38%152,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>69000</v>
+        <v>152952</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.39%163.5</t>
+          <t>-2.14%160</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>163.5</v>
+        <v>160</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.22%629,000</t>
+          <t>0.23%629,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:52</t>
+          <t>2026-10-20 22:20:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.2%2120</t>
+          <t>0%2120</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
